--- a/JP (Exclude Game)/Dialog/dialog.xlsx
+++ b/JP (Exclude Game)/Dialog/dialog.xlsx
@@ -5,13 +5,14 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="rumor" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="zone" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="unique" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="asmr" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="473">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -2375,6 +2376,205 @@
 That adventurer who believes in fate... so passionate, huh.
 An adventurer who... ‘inhales cats’? ...Wait, what?
 That witch’s bakery in Mysilia is so lovely... A real shop, right in the city. A witch... and a baker!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eyth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@2…ピー…
+@2…ザザザ…
+@2…ザザ…ガガ…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@2…bneep…
+@2…zzzzzz…
+@2…zshh…beep……</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@2…なで…なで…
+@2…ぎゅぅーっ…
+@2…ぎゅーーーーっ…
+@2…よし…よし…
+@2…ば…ばか…
+@2…か…勘違いしないでよね…
+@2…べ…べつに…あなたのためじゃ…
+@2…べ…べつに…
+@2…ひ…暇だっただけなんだからね…
+@2…んっ…っしょ…
+@2…い…癒やされなさい…
+@2…ふ…ふあぁぁ…
+@2…えっほ…えっほ…
+@2…迷える…ものたちよ…
+@2…い…癒やし…
+@2…傷ついた…魂を…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@2…p-pat…pat…
+@2…huuug…
+@2…huuuuuug…
+@2…there you go…there you go…
+@2…y-you idiot…
+@2…d-don’t get the wrong idea, okay…
+@2…i-it’s not like i’m doing this for you or anything…
+@2…i-it’s…really not…
+@2…i just…h-happened to have some time, that’s all…
+@2…mm…there…
+@2…y-you should…let yourself relax…
+@2…f-fuuaaah…
+@2…eh-ho…eh-ho…
+@2…oh…you who wander…
+@2…h-healing…
+@2…for your…wounded souls…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">opatos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@2…ゴリ…ゴリゴリ…
+@2…ゴゴゴゴ……
+@2…ズズズ……
+@2…ドシャァ……
+@2…ズシャッ…ズシャァ……
+@2…ガリ…ガリガリ……
+@2…ゴォ……ゴォォ……
+@2…ミシ…ミシミシ……
+@2…バキ……バキバキ……
+@2…ザラ……ザラザラ……
+@2…ゴン……ゴン……
+@2…ズン……ズゥン……
+@2…ドゥン……
+@2…フハハハハハハハ……
+@2…フハハ……フハァ……
+@2…フハーン……
+@2…フフ……フハ……
+@3フハハハハハハハハハハハハハ！ 
+@3フハーン
+@2…フフ……
+@2…フー…！…フー…！……</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@2…grrr…grind grind…
+@2…goooogoooo……
+@2…rumble……
+@2…crashhh……
+@2…shrrk…shraaa……
+@2…scrape…scrrrape……
+@2…gooo……grooo……
+@2…creak…craaack……
+@2…crack…crack crack……
+@2…grain…grind grind……
+@2…thud……thud……
+@2…boom……booom……
+@2…dunn……
+@2…muwahaha…
+@2…mwahahahaha…
+@2…muhan…
+@2…muwaha…muwaha…
+@3MUWAHAHAHAHAHAHAHA!
+@3MUHAN
+@2…muha……
+@2…mu…ha……mu…ha……</t>
+  </si>
+  <si>
+    <t xml:space="preserve">horome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@2…大丈夫…ママがちゃんとそばにいるからね…
+@2…おやすみ…いい子…
+@2…ママのお胸に…もたれてもいいよ…
+@2…ちゃんと生きてるだけで…えらい…
+@2…ほら…頭なでなで…安心して…
+@2…ほら…力を抜いて…
+@2…よしよし…
+@2…このまま…ぬくぬくしていきましょ…
+@2…なで…なで…力、抜いて…
+@2…ん…よしよし…いい子…
+@2…ぬくぬく…このまま…
+@2…もう…何も考えなくて…
+@2…ふわふわでしょう…落ち着くわね…
+@2…この尻尾…巻いてあげる…
+@2…ふわ…もふ…ほら…尻尾…
+@2…すり…すり…やさしく…巻くわね…
+@2…ぬく…ぬく…眠くなる…
+@2…そのまま…くっついて…
+@2…すぅ…はぁ…一緒に…呼吸…
+@2…ママだよ…
+@2…なで…なで…力…抜いて…
+@2…ほら…ぎゅううぅぅぅううっ…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@2…it’s okay…mommy’s right here with you…
+@2…good night…sweet one…
+@2…you can rest against mommy…it’s okay…
+@2…just being here…is already enough…
+@2…here…gentle head pats…you’re safe…
+@2…that’s it…relax…
+@2…there there…
+@2…let’s stay warm…just like this…
+@2…pat…pat…let it go…
+@2…mm…there there…good one…
+@2…warm…cozy…just like this…
+@2…no more thinking…now…
+@2…fluffy, isn’t it…it calms you…
+@2…i’ll wrap you…with my tail…
+@2…fluff…mofu…here…my tail…
+@2…rub…rub…gently…wrapping you…
+@2…warm…cozy…getting sleepy…
+@2…stay close…like that…
+@2…inhale…exhale…with me…
+@2…it’s mommy…
+@2…pat…pat…let it go…
+@2…there…huuuuuuuuuug…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">demitas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@2…ククク……
+@2…クク……
+@2…ク……ククク……
+@2…クク……クク…
+@2…ほら…還れ…
+@2…元素へ……
+@2…還れ…
+@2…元素へ…クク…
+@2…ク…ク…ク……
+@2…ク…ク…
+@2…クク…ク…
+@2…はやく…
+@2…クククク…
+@2…ククククク…
+@2…クク…クク…クク…
+@2………
+@2………
+@2……キウイ…クク…
+@2……
+@2…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@2…heh heh heh……
+@2…heh heh……
+@2…heh……heh heh……
+@2…heh heh……heh heh…
+@2…now… return…
+@2…to the elements……
+@2…return…
+@2…to the elements… heh heh…
+@2…heh… heh… heh……
+@2…heh… heh…
+@2…heh heh… heh…
+@2…hurry…
+@2…heh heh heh heh…
+@2…heh heh heh heh heh…
+@2…heh heh… heh heh… heh heh…
+@2………
+@2………
+@2……kiwi… heh heh…
+@2……
+@2… </t>
   </si>
 </sst>
 </file>
@@ -2629,9 +2829,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>38</xdr:col>
-      <xdr:colOff>281880</xdr:colOff>
+      <xdr:colOff>280800</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>120600</xdr:rowOff>
+      <xdr:rowOff>119520</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2641,7 +2841,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="49661280" cy="120600"/>
+          <a:ext cx="49660200" cy="119520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2915,7 +3115,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="true" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
         <v>34</v>
       </c>
@@ -4646,4 +4846,107 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="110.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="100.58"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C2" s="3"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="168.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="220.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="231.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="210.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>472</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>
--- a/JP (Exclude Game)/Dialog/dialog.xlsx
+++ b/JP (Exclude Game)/Dialog/dialog.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="485">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -2378,203 +2378,386 @@
 That witch’s bakery in Mysilia is so lovely... A real shop, right in the city. A witch... and a baker!</t>
   </si>
   <si>
+    <t xml:space="preserve">rodwyn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">私の料理に使われているのは全部最高級の素材。
+私のホウキコレクション、見てみたい？
+ええと…イモリの舌に…ハチの目。あら？ ごめんなさい、そこにいるのに気づかなかったわ。新しいレシピを考えていたの。
+あれ、この辺りにネコいなかった？
+もちろんパンは窯で焼けるわよ？ 
+薬棚？  ちゃんと見なさい、スパイスの棚でしょ！
+私の帽子？　ふふ、素敵でしょ？
+（魔女は虫が詰まっているような袋をミキシングボウルにどさっと入れた。）
+……質問が多いのねぇ…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I only use the highest quality ingredients for my baked goods.
+Would you like to see my broom collection?
+Let’s see…Tongue of newt. Eye of bee. Oh? Sorry, I didn’t notice you there. I was thinking of a new recipe.
+Have you seen any cats nearby?
+Of course you can bake bread in a kiln! Don’t you?
+My chemistry rack? Those are obviously spices!
+My hat? Cool right?
+(You watch her dump what appears to be a sack of bugs into a mixing bowl.) 
+You sure do ask a lot of questions…</t>
+  </si>
+  <si>
     <t xml:space="preserve">eyth</t>
   </si>
   <si>
-    <t xml:space="preserve">@2…ピー…
-@2…ザザザ…
-@2…ザザ…ガガ…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@2…bneep…
-@2…zzzzzz…
-@2…zshh…beep……</t>
+    <t xml:space="preserve">…ピー…
+…ザザザ…
+…ザザ…ガガ…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…bneep…
+…zzzzzz…
+…zshh…beep……</t>
   </si>
   <si>
     <t xml:space="preserve">jure</t>
   </si>
   <si>
-    <t xml:space="preserve">@2…なで…なで…
-@2…ぎゅぅーっ…
-@2…ぎゅーーーーっ…
-@2…よし…よし…
-@2…ば…ばか…
-@2…か…勘違いしないでよね…
-@2…べ…べつに…あなたのためじゃ…
-@2…べ…べつに…
-@2…ひ…暇だっただけなんだからね…
-@2…んっ…っしょ…
-@2…い…癒やされなさい…
-@2…ふ…ふあぁぁ…
-@2…えっほ…えっほ…
-@2…迷える…ものたちよ…
-@2…い…癒やし…
-@2…傷ついた…魂を…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@2…p-pat…pat…
-@2…huuug…
-@2…huuuuuug…
-@2…there you go…there you go…
-@2…y-you idiot…
-@2…d-don’t get the wrong idea, okay…
-@2…i-it’s not like i’m doing this for you or anything…
-@2…i-it’s…really not…
-@2…i just…h-happened to have some time, that’s all…
-@2…mm…there…
-@2…y-you should…let yourself relax…
-@2…f-fuuaaah…
-@2…eh-ho…eh-ho…
-@2…oh…you who wander…
-@2…h-healing…
-@2…for your…wounded souls…</t>
+    <t xml:space="preserve">…なで…なで…
+…ぎゅぅーっ…
+…ぎゅーーーーっ…
+…よし…よし…
+…ば…ばか…
+…か…勘違いしないでよね…
+…べ…べつに…あなたのためじゃ…
+…べ…べつに…
+…ひ…暇だっただけなんだからね…
+…んっ…っしょ…
+…い…癒やされなさい…
+…ふ…ふあぁぁ…
+…えっほ…えっほ…
+…迷える…ものたちよ…
+…い…癒やし…
+…傷ついた…魂を…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…p-pat…pat…
+…huuug…
+…huuuuuug…
+…there you go…there you go…
+…y-you idiot…
+…d-don’t get the wrong idea, okay…
+…i-it’s not like i’m doing this for you or anything…
+…i-it’s…really not…
+…i just…h-happened to have some time, that’s all…
+…mm…there…
+…y-you should…let yourself relax…
+…f-fuuaaah…
+…eh-ho…eh-ho…
+…oh…you who wander…
+…h-healing…
+…for your…wounded souls…</t>
   </si>
   <si>
     <t xml:space="preserve">opatos</t>
   </si>
   <si>
-    <t xml:space="preserve">@2…ゴリ…ゴリゴリ…
-@2…ゴゴゴゴ……
-@2…ズズズ……
-@2…ドシャァ……
-@2…ズシャッ…ズシャァ……
-@2…ガリ…ガリガリ……
-@2…ゴォ……ゴォォ……
-@2…ミシ…ミシミシ……
-@2…バキ……バキバキ……
-@2…ザラ……ザラザラ……
-@2…ゴン……ゴン……
-@2…ズン……ズゥン……
-@2…ドゥン……
-@2…フハハハハハハハ……
-@2…フハハ……フハァ……
-@2…フハーン……
-@2…フフ……フハ……
+    <t xml:space="preserve">…ゴリ…ゴリゴリ…
+…ゴゴゴゴ……
+…ズズズ……
+…ドシャァ……
+…ズシャッ…ズシャァ……
+…ガリ…ガリガリ……
+…ゴォ……ゴォォ……
+…ミシ…ミシミシ……
+…バキ……バキバキ……
+…ザラ……ザラザラ……
+…ゴン……ゴン……
+…ズン……ズゥン……
+…ドゥン……
+…フハハハハハハハ……
+…フハハ……フハァ……
+…フハーン……
+…フフ……フハ……
 @3フハハハハハハハハハハハハハ！ 
 @3フハーン
-@2…フフ……
-@2…フー…！…フー…！……</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@2…grrr…grind grind…
-@2…goooogoooo……
-@2…rumble……
-@2…crashhh……
-@2…shrrk…shraaa……
-@2…scrape…scrrrape……
-@2…gooo……grooo……
-@2…creak…craaack……
-@2…crack…crack crack……
-@2…grain…grind grind……
-@2…thud……thud……
-@2…boom……booom……
-@2…dunn……
-@2…muwahaha…
-@2…mwahahahaha…
-@2…muhan…
-@2…muwaha…muwaha…
+…フフ……
+…フー…！…フー…！……</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…grrr…grind grind…
+…goooogoooo……
+…rumble……
+…crashhh……
+…shrrk…shraaa……
+…scrape…scrrrape……
+…gooo……grooo……
+…creak…craaack……
+…crack…crack crack……
+…grain…grind grind……
+…thud……thud……
+…boom……booom……
+…dunn……
+…muwahaha…
+…mwahahahaha…
+…muhan…
+…muwaha…muwaha…
 @3MUWAHAHAHAHAHAHAHA!
 @3MUHAN
-@2…muha……
-@2…mu…ha……mu…ha……</t>
+…muha……
+…mu…ha……mu…ha……</t>
   </si>
   <si>
     <t xml:space="preserve">horome</t>
   </si>
   <si>
-    <t xml:space="preserve">@2…大丈夫…ママがちゃんとそばにいるからね…
-@2…おやすみ…いい子…
-@2…ママのお胸に…もたれてもいいよ…
-@2…ちゃんと生きてるだけで…えらい…
-@2…ほら…頭なでなで…安心して…
-@2…ほら…力を抜いて…
-@2…よしよし…
-@2…このまま…ぬくぬくしていきましょ…
-@2…なで…なで…力、抜いて…
-@2…ん…よしよし…いい子…
-@2…ぬくぬく…このまま…
-@2…もう…何も考えなくて…
-@2…ふわふわでしょう…落ち着くわね…
-@2…この尻尾…巻いてあげる…
-@2…ふわ…もふ…ほら…尻尾…
-@2…すり…すり…やさしく…巻くわね…
-@2…ぬく…ぬく…眠くなる…
-@2…そのまま…くっついて…
-@2…すぅ…はぁ…一緒に…呼吸…
-@2…ママだよ…
-@2…なで…なで…力…抜いて…
-@2…ほら…ぎゅううぅぅぅううっ…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@2…it’s okay…mommy’s right here with you…
-@2…good night…sweet one…
-@2…you can rest against mommy…it’s okay…
-@2…just being here…is already enough…
-@2…here…gentle head pats…you’re safe…
-@2…that’s it…relax…
-@2…there there…
-@2…let’s stay warm…just like this…
-@2…pat…pat…let it go…
-@2…mm…there there…good one…
-@2…warm…cozy…just like this…
-@2…no more thinking…now…
-@2…fluffy, isn’t it…it calms you…
-@2…i’ll wrap you…with my tail…
-@2…fluff…mofu…here…my tail…
-@2…rub…rub…gently…wrapping you…
-@2…warm…cozy…getting sleepy…
-@2…stay close…like that…
-@2…inhale…exhale…with me…
-@2…it’s mommy…
-@2…pat…pat…let it go…
-@2…there…huuuuuuuuuug…</t>
+    <t xml:space="preserve">…大丈夫…ママがちゃんとそばにいるからね…
+…おやすみ…いい子…
+…ママのお胸に…もたれてもいいよ…
+…ちゃんと生きてるだけで…えらい…
+…ほら…頭なでなで…安心して…
+…ほら…力を抜いて…
+…よしよし…
+…このまま…ぬくぬくしていきましょ…
+…なで…なで…力、抜いて…
+…ん…よしよし…いい子…
+…ぬくぬく…このまま…
+…もう…何も考えなくて…
+…ふわふわでしょう…落ち着くわね…
+…この尻尾…巻いてあげる…
+…ふわ…もふ…ほら…尻尾…
+…すり…すり…やさしく…巻くわね…
+…ぬく…ぬく…眠くなる…
+…そのまま…くっついて…
+…すぅ…はぁ…一緒に…呼吸…
+…ママだよ…
+…なで…なで…力…抜いて…
+…ほら…ぎゅううぅぅぅううっ…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…it’s okay…mommy’s right here with you…
+…good night…sweet one…
+…you can rest against mommy…it’s okay…
+…just being here…is already enough…
+…here…gentle head pats…you’re safe…
+…that’s it…relax…
+…there there…
+…let’s stay warm…just like this…
+…pat…pat…let it go…
+…mm…there there…good one…
+…warm…cozy…just like this…
+…no more thinking…now…
+…fluffy, isn’t it…it calms you…
+…i’ll wrap you…with my tail…
+…fluff…mofu…here…my tail…
+…rub…rub…gently…wrapping you…
+…warm…cozy…getting sleepy…
+…stay close…like that…
+…inhale…exhale…with me…
+…it’s mommy…
+…pat…pat…let it go…
+…there…huuuuuuuuuug…</t>
   </si>
   <si>
     <t xml:space="preserve">demitas</t>
   </si>
   <si>
-    <t xml:space="preserve">@2…ククク……
-@2…クク……
-@2…ク……ククク……
-@2…クク……クク…
-@2…ほら…還れ…
-@2…元素へ……
-@2…還れ…
-@2…元素へ…クク…
-@2…ク…ク…ク……
-@2…ク…ク…
-@2…クク…ク…
-@2…はやく…
-@2…クククク…
-@2…ククククク…
-@2…クク…クク…クク…
-@2………
-@2………
-@2……キウイ…クク…
-@2……
-@2…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@2…heh heh heh……
-@2…heh heh……
-@2…heh……heh heh……
-@2…heh heh……heh heh…
-@2…now… return…
-@2…to the elements……
-@2…return…
-@2…to the elements… heh heh…
-@2…heh… heh… heh……
-@2…heh… heh…
-@2…heh heh… heh…
-@2…hurry…
-@2…heh heh heh heh…
-@2…heh heh heh heh heh…
-@2…heh heh… heh heh… heh heh…
-@2………
-@2………
-@2……kiwi… heh heh…
-@2……
-@2… </t>
+    <t xml:space="preserve">…ククク……
+…クク……
+…ク……ククク……
+…クク……クク…
+…ほら…還れ…
+…元素へ……
+…還れ…
+…元素へ…クク…
+…ク…ク…ク……
+…ク…ク…
+…クク…ク…
+…はやく…
+…クククク…
+…ククククク…
+…クク…クク…クク…
+………
+………
+……キウイ…クク…
+……
+…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…heh heh heh……
+…heh heh……
+…heh……heh heh……
+…heh heh……heh heh…
+…now… return…
+…to the elements……
+…return…
+…to the elements… heh heh…
+…heh… heh… heh……
+…heh… heh…
+…heh heh… heh…
+…hurry…
+…heh heh heh heh…
+…heh heh heh heh heh…
+…heh heh… heh heh… heh heh…
+………
+………
+……kiwi… heh heh…
+……
+… </t>
+  </si>
+  <si>
+    <t xml:space="preserve">lulwy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…ふぅん…こういうのが好きなの…？
+…とんだ変態ね… 
+…この…豚野郎……アハハ……！
+…あら…震えてる……かわいそうに…
+…見下されるの…好きでしょう…？
+…虫ケラの分際で……アハハハ… 
+…小さい……ほんと……小さい……
+…アハ……笑えるわ……
+…アハハ……ミンチ……ミンチィ……！
+…哀れね……
+…ほら…もっと晒しなさい…
+…女神の前で…よくそんな顔できるわね…
+…アハハ…みじめな豚… 
+…その顔…最高に…無様ねぇ…
+…ほら…地面に這いつくばりなさい…
+…アハ…風も笑ってるわよ…
+…誰が…女神を見ていいって…言った…？
+…次に顔上げたら…ミンチよ…
+…アハッ…みじめな定命者ァ…
+…ほんと…分かりやすい…
+…アハハ…どうしようもないわね…
+…無様ね…罵られて…喜んじゃって…
+…この…変態…
+…ああ…今の…嬉しかったでしょ…？
+…ゴミが…
+…そのまま…無価値でいなさい…
+…ねえ…下心でもあるの…？
+…ああ…図星ね……アハハ！
+…存在してるだけで…不快…アハッ…
+…ほんと…救いようのない変態ね…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…oh… so this is what you like…?
+…what a degenerate…
+…you… filthy pig… ahaha…!
+…oh… you’re trembling… how adorable…
+…you like being looked down on… don’t you…?
+…a mere insect… ahahaha…
+…so small… truly… tiny…
+…aha… amusing…
+…ahaha… minced… so minced…!
+…pathetic…
+…come on… show me more…
+…making that face… in front of a goddess…
+…ahaha… pathetic pig…
+…that face… absolutely… disgraceful…
+…come on… crawl on the ground…
+…aha… the wind is laughing…
+…you think… you could look at a goddess…?
+…raise your head again… and you’re minced…
+…ahah… miserable mortal…
+…you’re… so easy to read…
+…ahaha… you’re hopeless…
+…pathetic… getting insulted… and enjoying it…
+…you… pervert…
+…ah… that just now… felt good, didn’t it…?
+…trash…
+…stay… worthless…
+…hey… do you have ulterior motives…?
+…ah… right on the mark…!
+…your mere existence… is irritating…aha…
+…truly… hopeless…pervert…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ehekatl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@3うみみゃあ！
+@3たらばがに！
+…スリ…
+…スリスリ…
+…ペロ…
+…ペロペロ…
+…コツン…
+…うみ…
+…みみみ…
+…み…</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">@3UMIMYAA!
+@3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">King crab!
+…rub…
+…rub rub…
+…lick…
+…lick lick…
+…bonk…
+…meo…
+…meo… w…
+…m… </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">fox_maid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…おはようございます、ご主人さま…
+…お茶をお持ちしますね…
+…ご不在の間、お屋敷のことは私がきちんとお預かりしていました…
+…わ、私だけ…家族の中で胸が控えめなのは嫌です…
+…脚立…どこにありましたっけ…？
+…あ…お顔に、何かついてますよ…
+…ご主人さまの代わりに…私がやりますから…
+…あとどれくらい…お餅をつけばいいんでしょう…？
+…きゃあっ！…
+…ご、ご主人さま…！
+…お世話するのはメイドとしての務めですけど……たとえそうじゃなくても、私はします…
+…今夜のご夕食は…何になさいますか、ご主人さま…？
+…はい、あーん…♥
+…スッポンは…滋養にいいって聞きました…
+…高い棚のもの、抱き上げなくても大丈夫ですよ…？
+…ご主人さまとこんなに近いと…メイドとして、少し落ち着きません…
+…ちゃんと運動もしてくださいね…？
+…私…ちゃんとできてましたか、ご主人さま…？
+…ミ、ミルクですか…？ そ、それは……</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…Good morning, Master…
+…Allow me to serve you your tea…
+…I've stewarded your affairs while you were away…
+…I don't want to be the only flat one in my family…
+…Have you seen the stepladder…?
+…You have something on your face…
+…I'll gladly do it so you don't have to…
+…How much more mochi do I have to pound…?
+…Kyaaa!…
+…M-master…!
+…It's my duty to take care of you…but even if it weren't, I'd do it anyway…
+…What would you like for dinner tonight, Master…?
+…Open wide~♥
+…I've heard soft-shelled turtle is good for stamina…
+…You don't have to lift me so I can reach the high shelf…
+…It feels awkward to be this close with you when I'm your maid…
+…Be sure to get some exercise, okay…?
+…Did I do a good job, Master…?
+…Milk? B-but…</t>
   </si>
 </sst>
 </file>
@@ -2829,9 +3012,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>38</xdr:col>
-      <xdr:colOff>280800</xdr:colOff>
+      <xdr:colOff>278280</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>119520</xdr:rowOff>
+      <xdr:rowOff>117000</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2841,7 +3024,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="49660200" cy="119520"/>
+          <a:ext cx="49657680" cy="117000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4326,13 +4509,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.58"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.56"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="110.96"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="100.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="139.81"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4358,7 +4541,7 @@
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4" s="3"/>
     </row>
-    <row r="5" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>330</v>
       </c>
@@ -4402,7 +4585,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
         <v>342</v>
       </c>
@@ -4413,7 +4596,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>345</v>
       </c>
@@ -4490,7 +4673,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
         <v>366</v>
       </c>
@@ -4501,7 +4684,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
         <v>369</v>
       </c>
@@ -4601,7 +4784,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="79.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
         <v>396</v>
       </c>
@@ -4612,7 +4795,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="55.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
         <v>399</v>
       </c>
@@ -4667,7 +4850,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
         <v>413</v>
       </c>
@@ -4689,7 +4872,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
         <v>419</v>
       </c>
@@ -4737,7 +4920,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
         <v>431</v>
       </c>
@@ -4782,7 +4965,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="9" t="s">
         <v>443</v>
       </c>
@@ -4793,7 +4976,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="9" t="s">
         <v>446</v>
       </c>
@@ -4804,7 +4987,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="9" t="s">
         <v>449</v>
       </c>
@@ -4815,7 +4998,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="9" t="s">
         <v>452</v>
       </c>
@@ -4835,6 +5018,17 @@
       </c>
       <c r="D47" s="3" t="s">
         <v>457</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>460</v>
       </c>
     </row>
   </sheetData>
@@ -4853,7 +5047,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.58"/>
@@ -4887,57 +5081,90 @@
     </row>
     <row r="5" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="168.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="220.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="231.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="210.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>472</v>
+        <v>475</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="314.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="112.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="199.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>484</v>
       </c>
     </row>
   </sheetData>

--- a/JP (Exclude Game)/Dialog/dialog.xlsx
+++ b/JP (Exclude Game)/Dialog/dialog.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" state="visible" r:id="rId3"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="509">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -315,6 +315,15 @@
   </si>
   <si>
     <t xml:space="preserve">tail3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tail4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">どうした{のだ}、#pc？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Why are you looking at me, #pc?</t>
   </si>
   <si>
     <t xml:space="preserve">lockpick_purse</t>
@@ -737,6 +746,51 @@
   </si>
   <si>
     <t xml:space="preserve">...Do you recall when I told you, 'Don't lose it'? Here’s another, so take care of it this time.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">marry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">はい…喜んで。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes...with pleasure.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wedding_deed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">嬉しい{よ}。でも、挙式許可証が必要な{のだ}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">That makes me happy. But we need a Wedding Permit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wedding_zone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">嬉しい{よ}。でも、拠点でゆっくり話そう{よ}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">That makes me happy. But let's take our time and talk at home.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wedding_confirm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">本当に？（現在のパーティーは解散され、#tgと二人きりのパーティーが編成される）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Are you serious? (Your current party is disbanded, and a new party is formed with just you and #tg.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wedding_accept</t>
+  </si>
+  <si>
+    <t xml:space="preserve">嬉しい{よ}、#pc！ 私はとても幸せ{だ}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I'm so happy, #pc! I'm truly happy.</t>
   </si>
   <si>
     <t xml:space="preserve">default</t>
@@ -1133,6 +1187,57 @@
 How may I serve you today?</t>
   </si>
   <si>
+    <t xml:space="preserve">bottle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">リュシア|帰らぬ船|この瓶が誰かの手に届くなら、私はもう海の底でしょう。けれど空はとても青かった。
+名もなき兵士|最後の手紙|剣より重いのは恐怖だった。それでも私は逃げなかったと、誰かに知ってほしい。
+エルネス|潮騒の祈り|神よ、波を鎮める力がないなら、せめて眠りをください。
+ミレイユ|約束の浜辺|先に着いたら火を焚いて待っているわ。迷わず来て。
+航海士ダロス|星の記録|星は今日も正しかった。間違えたのは私だ。
+セレナ|ささやかな告白|あなたの名前を声に出せなかった。それだけが心残りです。
+老人|若き日へ|海は奪うが、すべてを無駄にはしない。生き延びろ。
+双子の妹|半分の世界|兄さん、世界はまだ半分残っているよ。だから帰ってきて。
+船医レナート|診療記録|傷は治せなかったが、痛みは和らげられた。それで十分だ。
+イザベル|歌の続きを|私がいなくても、この歌を最後まで歌って。
+密輸人カイル|報酬の行方|金は北の入り江に沈めた。欲しければ潜れ。
+神官見習いロア|疑いの告白|祈りは届かなかった。それでも私は祈ることをやめない。
+漁師ハルド|最後の漁|今日の獲物はなかった。でも海と話はできた。
+旅人シアン|通過点|ここは終わりじゃない。ただの通過点だ。
+王国書記官|公式記録抄|本船は嵐により喪失。以上。
+母|子へ|寒くなったら外套を着なさい。約束よ。
+吟遊詩人フェイ|未完成の詩|韻が足りない。続きを考えてくれる人へ。
+傭兵団長ヴォルク|撤退命令|生きて帰れ。名誉は後で拾えばいい。
+少女|はじめての旅|少し怖い。でも楽しい。
+誰か|拾ったあなたへ|あなたがこれを読んでいるなら、世界はまだ続いている。
+不明|お…|おうち…かえう…！
+不明|もう…|もうだめぽ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lucia|The Ship That Never Returned|If this bottle reaches someone,I will likely be beneath the sea by then.But the sky was very blue.
+An Unnamed Soldier|Final Letter|Fear weighed heavier than my sword.But I want someone to know I did not run.
+Ernes|Prayer of the Surf|God,if you cannot calm the waves,then at least grant me sleep.
+Mireille|The Promised Shore|If I arrive first,I will light a fire and wait.Come without losing your way.
+Navigator Daros|Record of the Stars|The stars were correct again today.The one who erred was me.
+Selena|A Small Confession|I could never speak your name aloud.That is my only regret.
+Old Man|To My Younger Days|The sea takes much,but nothing is entirely wasted.Survive.
+The Younger Twin|Half the World Left|Brother,half the world is still here.So please come back.
+Ship Doctor Renato|Medical Notes|I could not heal the wounds,but I eased the pain.That was enough.
+Isabelle|Finish the Song|Even if I am gone,please sing this song to the end.
+Smuggler Kyle|Where the Payment Lies|The gold is sunk in the northern cove.Dive if you want it.
+Acolyte Roa|Confession of Doubt|My prayers were unanswered.Still,I will not stop praying.
+Fisherman Hald|The Last Catch|There was no catch today.But I spoke with the sea.
+Traveler Cyan|A Passing Point|This is not the end.It is only a passing point.
+Royal Scribe|Excerpt from Official Records|The vessel was lost to the storm.End of report.
+Mother|To My Child|Put on your cloak when it gets cold.Promise me.
+Bard Fey|An Unfinished Poem|The rhyme is missing.To whoever finishes it.
+Mercenary Captain Volk|Order to Retreat|Come back alive.Honor can be picked up later.
+Little Girl|My First Journey|I'm a little scared.But it's fun.
+Someone|To Whoever Finds This|If you are reading this,the world is still going on.
+Unknown|I...|I'm...going...home...!
+Unknown|I'm...|Moudamepo</t>
+  </si>
+  <si>
     <t xml:space="preserve">mysilia</t>
   </si>
   <si>
@@ -1417,6 +1522,23 @@
 Our great father oversees our penance, and there is no escape from our fates.
 As time passes, we grow less concerned with our material conditions...
 Yes #race, you're standing in front of an exile who has lived more than 1000 years.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mimu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">……ぴ？
+…………ぴぴ
+ピ………
+…ピぽ………
+……ぴ……エラー……</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…Pi?
+……Pipi
+Pi………
+…Pipo………
+……Pi……Error……</t>
   </si>
   <si>
     <t xml:space="preserve">namamani</t>
@@ -3012,9 +3134,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>38</xdr:col>
-      <xdr:colOff>278280</xdr:colOff>
+      <xdr:colOff>275760</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>117000</xdr:rowOff>
+      <xdr:rowOff>114480</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3024,7 +3146,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="49657680" cy="117000"/>
+          <a:ext cx="49655160" cy="114480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3162,7 +3284,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D82"/>
+  <dimension ref="A1:D88"/>
   <sheetFormatPr defaultColWidth="14.390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.11"/>
@@ -3600,7 +3722,7 @@
       <c r="A42" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C42" s="1" t="s">
         <v>112</v>
       </c>
       <c r="D42" s="1" t="s">
@@ -3680,22 +3802,22 @@
       <c r="C49" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="D49" s="4" t="s">
+      <c r="D49" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
         <v>135</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="D50" s="4" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
         <v>138</v>
       </c>
@@ -3728,7 +3850,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
         <v>147</v>
       </c>
@@ -3750,7 +3872,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
         <v>153</v>
       </c>
@@ -3761,7 +3883,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
         <v>156</v>
       </c>
@@ -3790,7 +3912,7 @@
       <c r="C59" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="D59" s="4" t="s">
+      <c r="D59" s="1" t="s">
         <v>164</v>
       </c>
     </row>
@@ -3801,7 +3923,7 @@
       <c r="C60" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="D60" s="1" t="s">
+      <c r="D60" s="4" t="s">
         <v>167</v>
       </c>
     </row>
@@ -3823,7 +3945,7 @@
       <c r="C62" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="D62" s="3" t="s">
+      <c r="D62" s="1" t="s">
         <v>173</v>
       </c>
     </row>
@@ -3834,7 +3956,7 @@
       <c r="C63" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="D63" s="4" t="s">
+      <c r="D63" s="3" t="s">
         <v>176</v>
       </c>
     </row>
@@ -3845,7 +3967,7 @@
       <c r="C64" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="D64" s="1" t="s">
+      <c r="D64" s="4" t="s">
         <v>179</v>
       </c>
     </row>
@@ -3889,12 +4011,12 @@
       <c r="C68" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="D68" s="3" t="s">
+      <c r="D68" s="1" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="3" t="s">
+      <c r="A69" s="1" t="s">
         <v>192</v>
       </c>
       <c r="C69" s="3" t="s">
@@ -3904,8 +4026,8 @@
         <v>194</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="1" t="s">
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="3" t="s">
         <v>195</v>
       </c>
       <c r="C70" s="3" t="s">
@@ -3926,14 +4048,14 @@
         <v>200</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="C72" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="D72" s="1" t="s">
+      <c r="D72" s="3" t="s">
         <v>203</v>
       </c>
     </row>
@@ -3952,10 +4074,10 @@
       <c r="A74" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="C74" s="3" t="s">
+      <c r="C74" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="D74" s="4" t="s">
+      <c r="D74" s="1" t="s">
         <v>209</v>
       </c>
     </row>
@@ -3974,7 +4096,7 @@
       <c r="A76" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="C76" s="3" t="s">
         <v>214</v>
       </c>
       <c r="D76" s="4" t="s">
@@ -3992,18 +4114,18 @@
         <v>218</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="C78" s="3" t="s">
+      <c r="C78" s="1" t="s">
         <v>220</v>
       </c>
       <c r="D78" s="4" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
         <v>222</v>
       </c>
@@ -4018,7 +4140,7 @@
       <c r="A80" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C80" s="3" t="s">
         <v>226</v>
       </c>
       <c r="D80" s="4" t="s">
@@ -4045,6 +4167,72 @@
       </c>
       <c r="D82" s="4" t="s">
         <v>233</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>251</v>
       </c>
     </row>
   </sheetData>
@@ -4064,7 +4252,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="13.63"/>
@@ -4098,213 +4286,224 @@
     </row>
     <row r="5" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>242</v>
+        <v>260</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>245</v>
+        <v>263</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>247</v>
+        <v>265</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>251</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>256</v>
+        <v>274</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>262</v>
+        <v>280</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>263</v>
+        <v>281</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>264</v>
+        <v>282</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>266</v>
+        <v>284</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>267</v>
+        <v>285</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>268</v>
+        <v>286</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>269</v>
+        <v>287</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>271</v>
+        <v>289</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>272</v>
+        <v>290</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>274</v>
+        <v>292</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>275</v>
+        <v>293</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="200.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8" t="s">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="E19" s="1"/>
     </row>
     <row r="20" customFormat="false" ht="168.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>281</v>
+        <v>299</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="241.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>282</v>
+        <v>300</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>286</v>
+        <v>304</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>290</v>
+        <v>308</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="231.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -4348,149 +4547,149 @@
     </row>
     <row r="5" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>292</v>
+        <v>313</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>293</v>
+        <v>314</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>295</v>
+        <v>316</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>296</v>
+        <v>317</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>297</v>
+        <v>318</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>298</v>
+        <v>319</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>299</v>
+        <v>320</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>300</v>
+        <v>321</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>301</v>
+        <v>322</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>302</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>303</v>
+        <v>324</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>304</v>
+        <v>325</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>305</v>
+        <v>326</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>306</v>
+        <v>327</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>307</v>
+        <v>328</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>308</v>
+        <v>329</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>309</v>
+        <v>330</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>310</v>
+        <v>331</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>312</v>
+        <v>333</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>313</v>
+        <v>334</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>316</v>
+        <v>337</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="3" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>320</v>
+        <v>341</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="147.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="3" t="s">
-        <v>322</v>
+        <v>343</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>323</v>
+        <v>344</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>324</v>
+        <v>345</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="3" t="s">
-        <v>325</v>
+        <v>346</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>326</v>
+        <v>347</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="168.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="3" t="s">
-        <v>328</v>
+        <v>349</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>329</v>
+        <v>350</v>
       </c>
     </row>
   </sheetData>
@@ -4509,7 +4708,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.58"/>
@@ -4541,494 +4740,505 @@
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4" s="3"/>
     </row>
-    <row r="5" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>330</v>
+        <v>351</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>331</v>
+        <v>352</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>333</v>
+        <v>354</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="s">
-        <v>336</v>
+        <v>355</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>357</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>339</v>
+        <v>358</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="9" t="s">
+        <v>360</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>340</v>
+        <v>361</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>341</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>342</v>
+        <v>363</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>343</v>
+        <v>364</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>345</v>
+        <v>366</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>346</v>
+        <v>367</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>348</v>
+        <v>369</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>349</v>
+        <v>370</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>351</v>
+        <v>372</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>352</v>
+        <v>373</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>354</v>
+        <v>375</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>355</v>
+        <v>376</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>357</v>
+        <v>378</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>360</v>
+        <v>381</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>361</v>
+        <v>382</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>363</v>
+        <v>384</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>364</v>
+        <v>385</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>366</v>
+        <v>387</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>367</v>
+        <v>388</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="B18" s="3"/>
+        <v>390</v>
+      </c>
       <c r="C18" s="3" t="s">
-        <v>370</v>
+        <v>391</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>372</v>
-      </c>
+        <v>393</v>
+      </c>
+      <c r="B19" s="3"/>
       <c r="C19" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>394</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>375</v>
+        <v>396</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>397</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>379</v>
+        <v>400</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>380</v>
+        <v>401</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>381</v>
+        <v>402</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>382</v>
+        <v>403</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>383</v>
+        <v>404</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>384</v>
+        <v>405</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>385</v>
+        <v>406</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>387</v>
+        <v>408</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>388</v>
+        <v>409</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>390</v>
+        <v>411</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>391</v>
+        <v>412</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>393</v>
+        <v>414</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>394</v>
+        <v>415</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="79.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>396</v>
+        <v>417</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="D27" s="10" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>418</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="79.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>399</v>
+        <v>420</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>421</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>403</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="179.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>423</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="9" t="s">
-        <v>408</v>
+        <v>426</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>427</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="179.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>429</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>409</v>
+        <v>430</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="s">
-        <v>410</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>411</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>432</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
-        <v>413</v>
-      </c>
-      <c r="C33" s="12" t="s">
-        <v>414</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="3" t="s">
-        <v>419</v>
-      </c>
-      <c r="B35" s="5"/>
+        <v>434</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>435</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>438</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="s">
+        <v>440</v>
+      </c>
       <c r="C35" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>441</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>422</v>
+        <v>443</v>
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="3" t="s">
-        <v>423</v>
+        <v>444</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>424</v>
+        <v>445</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>425</v>
+        <v>446</v>
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="3" t="s">
-        <v>426</v>
+        <v>447</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>428</v>
+        <v>449</v>
       </c>
       <c r="B38" s="5"/>
-      <c r="C38" s="5" t="s">
-        <v>429</v>
+      <c r="C38" s="3" t="s">
+        <v>450</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>431</v>
+        <v>452</v>
       </c>
       <c r="B39" s="5"/>
-      <c r="C39" s="3" t="s">
-        <v>432</v>
+      <c r="C39" s="5" t="s">
+        <v>453</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="s">
-        <v>434</v>
-      </c>
+        <v>454</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="B40" s="5"/>
       <c r="C40" s="3" t="s">
-        <v>435</v>
+        <v>456</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>436</v>
+        <v>457</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>437</v>
+        <v>458</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>438</v>
+        <v>459</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>439</v>
+        <v>460</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="9" t="s">
-        <v>440</v>
+      <c r="A42" s="1" t="s">
+        <v>461</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>441</v>
+        <v>462</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>442</v>
+        <v>463</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="9" t="s">
-        <v>443</v>
+        <v>464</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>444</v>
+        <v>465</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="9" t="s">
-        <v>446</v>
+        <v>467</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>447</v>
+        <v>468</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="9" t="s">
-        <v>449</v>
+        <v>470</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>450</v>
+        <v>471</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="9" t="s">
-        <v>452</v>
+        <v>473</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>453</v>
+        <v>474</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>454</v>
+        <v>475</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="9" t="s">
-        <v>455</v>
+        <v>476</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>456</v>
+        <v>477</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1" t="s">
-        <v>458</v>
+        <v>478</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="9" t="s">
+        <v>479</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>459</v>
+        <v>480</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>460</v>
+        <v>481</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>484</v>
       </c>
     </row>
   </sheetData>
@@ -5081,90 +5291,90 @@
     </row>
     <row r="5" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>461</v>
+        <v>485</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>462</v>
+        <v>486</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>463</v>
+        <v>487</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="168.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>464</v>
+        <v>488</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>465</v>
+        <v>489</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>466</v>
+        <v>490</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="220.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>467</v>
+        <v>491</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>468</v>
+        <v>492</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>469</v>
+        <v>493</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="231.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>470</v>
+        <v>494</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>471</v>
+        <v>495</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>472</v>
+        <v>496</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="210.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>473</v>
+        <v>497</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>474</v>
+        <v>498</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>475</v>
+        <v>499</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="314.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>476</v>
+        <v>500</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>477</v>
+        <v>501</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>478</v>
+        <v>502</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="112.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>479</v>
+        <v>503</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>481</v>
+        <v>505</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="199.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>483</v>
+        <v>507</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>484</v>
+        <v>508</v>
       </c>
     </row>
   </sheetData>

--- a/JP (Exclude Game)/Dialog/dialog.xlsx
+++ b/JP (Exclude Game)/Dialog/dialog.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="524">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -791,6 +791,87 @@
   </si>
   <si>
     <t xml:space="preserve">I'm so happy, #pc! I'm truly happy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rob1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">見損なった{よ}！
+ひどい{よ}、やめて{くれ}！
+返り討ちにしてくれる{よ}。
+ごろつき風情に何ができるという{のだ}？
+やめて{くれ}。きっと後悔する{よ}。
+傭兵さんたち、このごろつきを追い払って{くれ}。
+ふん、この護衛の数が見えないの{か}？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I misjudged you!
+Please, stop this!
+You'll regret coming after me.
+What makes you think a common thug can take me on?
+Please stop. You'll regret this.
+Mercenaries, drive this ruffian off.
+Hmph. Can't you see how many guards I have?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mama_yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ママだよ！
+{はい}、ママ{だ}～！
+ママはここにいる{のだ}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mommy's here!
+Yes, I'm your mommy!
+Mommy is right here.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mama_no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">シッシッ！
+ママじゃない{よ}！
+君は何を言っている{のだ}？
+かわいそうに…頭を打ったの{か}？
+気持ち悪い{よ}…
+え…？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shoo, shoo!
+I'm not your mom!
+What are you talking about...?
+How pitiful... did you hit your head?
+That’s creepy...
+Huh...? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">baby_yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ママー！
+私の…ママなの{か}？
+マ…ママ…？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mommy!
+...You are my...mommy?
+Ma... mama...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">baby_no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">こんなのママじゃない{よ}！
+君は何を言っている{のだ}？
+かわいそうに…頭を打ったの{か}？
+え…？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You're not my mommy!
+What are you talking about...?
+How pitiful... did you hit your head?
+Huh...? </t>
   </si>
   <si>
     <t xml:space="preserve">default</t>
@@ -3134,9 +3215,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>38</xdr:col>
-      <xdr:colOff>275760</xdr:colOff>
+      <xdr:colOff>274320</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>114480</xdr:rowOff>
+      <xdr:rowOff>113040</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3146,7 +3227,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="49655160" cy="114480"/>
+          <a:ext cx="49653720" cy="113040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3284,7 +3365,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D93"/>
   <sheetFormatPr defaultColWidth="14.390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.11"/>
@@ -4233,6 +4314,61 @@
       </c>
       <c r="D88" s="4" t="s">
         <v>251</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -4286,224 +4422,224 @@
     </row>
     <row r="5" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>253</v>
+        <v>268</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>254</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>257</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>263</v>
+        <v>278</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>266</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>268</v>
+        <v>283</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>272</v>
+        <v>287</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>276</v>
+        <v>291</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>277</v>
+        <v>292</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>278</v>
+        <v>293</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>279</v>
+        <v>294</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>284</v>
+        <v>299</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>287</v>
+        <v>302</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>289</v>
+        <v>304</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>293</v>
+        <v>308</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="200.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>294</v>
+        <v>309</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8" t="s">
-        <v>295</v>
+        <v>310</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="E19" s="1"/>
     </row>
     <row r="20" customFormat="false" ht="168.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="241.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>300</v>
+        <v>315</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>302</v>
+        <v>317</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>307</v>
+        <v>322</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>308</v>
+        <v>323</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="231.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
     </row>
   </sheetData>
@@ -4547,149 +4683,149 @@
     </row>
     <row r="5" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>314</v>
+        <v>329</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>316</v>
+        <v>331</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>317</v>
+        <v>332</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>318</v>
+        <v>333</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>320</v>
+        <v>335</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>322</v>
+        <v>337</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>329</v>
+        <v>344</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>332</v>
+        <v>347</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>334</v>
+        <v>349</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>335</v>
+        <v>350</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>338</v>
+        <v>353</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>339</v>
+        <v>354</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="3" t="s">
-        <v>340</v>
+        <v>355</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>341</v>
+        <v>356</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="147.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="3" t="s">
-        <v>343</v>
+        <v>358</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>344</v>
+        <v>359</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="3" t="s">
-        <v>346</v>
+        <v>361</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>347</v>
+        <v>362</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="168.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>348</v>
+        <v>363</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="3" t="s">
-        <v>349</v>
+        <v>364</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>350</v>
+        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -4742,308 +4878,308 @@
     </row>
     <row r="5" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>351</v>
+        <v>366</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>352</v>
+        <v>367</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>353</v>
+        <v>368</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>354</v>
+        <v>369</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>355</v>
+        <v>370</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>356</v>
+        <v>371</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>357</v>
+        <v>372</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>358</v>
+        <v>373</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>359</v>
+        <v>374</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>360</v>
+        <v>375</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>361</v>
+        <v>376</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>362</v>
+        <v>377</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>363</v>
+        <v>378</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>364</v>
+        <v>379</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>365</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>366</v>
+        <v>381</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>367</v>
+        <v>382</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>368</v>
+        <v>383</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>369</v>
+        <v>384</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>370</v>
+        <v>385</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>371</v>
+        <v>386</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>372</v>
+        <v>387</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>373</v>
+        <v>388</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>374</v>
+        <v>389</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>375</v>
+        <v>390</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>376</v>
+        <v>391</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>377</v>
+        <v>392</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>378</v>
+        <v>393</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>379</v>
+        <v>394</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>380</v>
+        <v>395</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>381</v>
+        <v>396</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>382</v>
+        <v>397</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>383</v>
+        <v>398</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>384</v>
+        <v>399</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>385</v>
+        <v>400</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>386</v>
+        <v>401</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>387</v>
+        <v>402</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>389</v>
+        <v>404</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>390</v>
+        <v>405</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>391</v>
+        <v>406</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>392</v>
+        <v>407</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>393</v>
+        <v>408</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3" t="s">
-        <v>394</v>
+        <v>409</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>395</v>
+        <v>410</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>397</v>
+        <v>412</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>398</v>
+        <v>413</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>399</v>
+        <v>414</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>400</v>
+        <v>415</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>401</v>
+        <v>416</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>402</v>
+        <v>417</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>403</v>
+        <v>418</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>404</v>
+        <v>419</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>405</v>
+        <v>420</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>406</v>
+        <v>421</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>407</v>
+        <v>422</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>408</v>
+        <v>423</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>409</v>
+        <v>424</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>410</v>
+        <v>425</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>411</v>
+        <v>426</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>412</v>
+        <v>427</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>413</v>
+        <v>428</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>414</v>
+        <v>429</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>415</v>
+        <v>430</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>416</v>
+        <v>431</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>417</v>
+        <v>432</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>418</v>
+        <v>433</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>419</v>
+        <v>434</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="79.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>421</v>
+        <v>436</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>422</v>
+        <v>437</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>423</v>
+        <v>438</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>424</v>
+        <v>439</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>425</v>
+        <v>440</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>427</v>
+        <v>442</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>428</v>
+        <v>443</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="179.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>429</v>
+        <v>444</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>430</v>
+        <v>445</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>431</v>
+        <v>446</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="s">
-        <v>432</v>
+        <v>447</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>433</v>
+        <v>448</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>206</v>
@@ -5051,194 +5187,194 @@
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
-        <v>434</v>
+        <v>449</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>435</v>
+        <v>450</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>436</v>
+        <v>451</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="9" t="s">
-        <v>437</v>
+        <v>452</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>438</v>
+        <v>453</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>439</v>
+        <v>454</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>440</v>
+        <v>455</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>441</v>
+        <v>456</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>442</v>
+        <v>457</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>443</v>
+        <v>458</v>
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="3" t="s">
-        <v>444</v>
+        <v>459</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>445</v>
+        <v>460</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>446</v>
+        <v>461</v>
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="3" t="s">
-        <v>447</v>
+        <v>462</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>448</v>
+        <v>463</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>449</v>
+        <v>464</v>
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="3" t="s">
-        <v>450</v>
+        <v>465</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>451</v>
+        <v>466</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>452</v>
+        <v>467</v>
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5" t="s">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>454</v>
+        <v>469</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>455</v>
+        <v>470</v>
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="3" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>457</v>
+        <v>472</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>458</v>
+        <v>473</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>459</v>
+        <v>474</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>460</v>
+        <v>475</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>461</v>
+        <v>476</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>462</v>
+        <v>477</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>463</v>
+        <v>478</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="9" t="s">
-        <v>464</v>
+        <v>479</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>465</v>
+        <v>480</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>466</v>
+        <v>481</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="9" t="s">
-        <v>467</v>
+        <v>482</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>468</v>
+        <v>483</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>469</v>
+        <v>484</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="9" t="s">
-        <v>470</v>
+        <v>485</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>471</v>
+        <v>486</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>472</v>
+        <v>487</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="9" t="s">
-        <v>473</v>
+        <v>488</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>474</v>
+        <v>489</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>475</v>
+        <v>490</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="9" t="s">
-        <v>476</v>
+        <v>491</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>477</v>
+        <v>492</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>478</v>
+        <v>493</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="9" t="s">
-        <v>479</v>
+        <v>494</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>480</v>
+        <v>495</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>481</v>
+        <v>496</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>482</v>
+        <v>497</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>483</v>
+        <v>498</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>484</v>
+        <v>499</v>
       </c>
     </row>
   </sheetData>
@@ -5291,90 +5427,90 @@
     </row>
     <row r="5" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>485</v>
+        <v>500</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>486</v>
+        <v>501</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>487</v>
+        <v>502</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="168.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>488</v>
+        <v>503</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>489</v>
+        <v>504</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>490</v>
+        <v>505</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="220.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>491</v>
+        <v>506</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>492</v>
+        <v>507</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>493</v>
+        <v>508</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="231.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>494</v>
+        <v>509</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>495</v>
+        <v>510</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="210.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>497</v>
+        <v>512</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>498</v>
+        <v>513</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>499</v>
+        <v>514</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="314.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>500</v>
+        <v>515</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>501</v>
+        <v>516</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>502</v>
+        <v>517</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="112.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>504</v>
+        <v>519</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="199.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>506</v>
+        <v>521</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>507</v>
+        <v>522</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>508</v>
+        <v>523</v>
       </c>
     </row>
   </sheetData>

--- a/JP (Exclude Game)/Dialog/dialog.xlsx
+++ b/JP (Exclude Game)/Dialog/dialog.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" state="visible" r:id="rId3"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="527">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -1620,6 +1620,25 @@
 Pi………
 …Pipo………
 ……Pi……Error……</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mamani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">人間の行動は、常に感情の誤作動に導かれる。
+機械はやがて人間の代わりに地上を支配するだろう。
+あの戦狂いの祭壇は、いつからここにあるんだ？
+生身だった頃の私の体が、まだ地上に残っているようだ。
+くだらないな。人間界も、神界も。
+神という存在は非合理的だ。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Human behavior is always guided by the malfunction of emotion.
+One day, machines will rule the earth in place of humankind.
+How long has that warmonger's altar been here?
+It seems my old body still remains on the surface.
+How absurd. The realm of humans, the realm of gods, all of it.
+The very existence of gods is irrational.</t>
   </si>
   <si>
     <t xml:space="preserve">namamani</t>
@@ -3215,9 +3234,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>38</xdr:col>
-      <xdr:colOff>274320</xdr:colOff>
+      <xdr:colOff>273960</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>113040</xdr:rowOff>
+      <xdr:rowOff>112680</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3227,7 +3246,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="49653720" cy="113040"/>
+          <a:ext cx="49653360" cy="112680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4844,7 +4863,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.58"/>
@@ -4887,7 +4906,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>369</v>
       </c>
@@ -4898,30 +4917,30 @@
         <v>371</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>372</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="s">
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>375</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="4" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+    <row r="9" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="9" t="s">
         <v>378</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -4942,7 +4961,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>384</v>
       </c>
@@ -4953,7 +4972,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
         <v>387</v>
       </c>
@@ -4964,7 +4983,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
         <v>390</v>
       </c>
@@ -4975,7 +4994,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
         <v>393</v>
       </c>
@@ -4986,7 +5005,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
         <v>396</v>
       </c>
@@ -4997,7 +5016,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
         <v>399</v>
       </c>
@@ -5008,7 +5027,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
         <v>402</v>
       </c>
@@ -5019,7 +5038,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
         <v>405</v>
       </c>
@@ -5030,11 +5049,10 @@
         <v>407</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="B19" s="3"/>
       <c r="C19" s="3" t="s">
         <v>409</v>
       </c>
@@ -5042,29 +5060,30 @@
         <v>410</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
         <v>411</v>
       </c>
+      <c r="B20" s="3"/>
       <c r="C20" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="3" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
         <v>414</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" s="1" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
         <v>417</v>
       </c>
@@ -5097,7 +5116,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
         <v>426</v>
       </c>
@@ -5108,7 +5127,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
         <v>429</v>
       </c>
@@ -5119,7 +5138,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
         <v>432</v>
       </c>
@@ -5130,107 +5149,106 @@
         <v>434</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="79.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
         <v>435</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D28" s="3" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="79.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
         <v>438</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="D29" s="10" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C30" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D30" s="3" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="179.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="10" t="s">
         <v>445</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="D31" s="1" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="9" t="s">
+    <row r="32" customFormat="false" ht="179.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
         <v>447</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>448</v>
       </c>
       <c r="D32" s="3" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="9" t="s">
-        <v>449</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>450</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="9" t="s">
         <v>452</v>
       </c>
-      <c r="C34" s="12" t="s">
+      <c r="C34" s="11" t="s">
         <v>453</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D34" s="1" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="s">
+    <row r="35" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="9" t="s">
         <v>455</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="12" t="s">
         <v>456</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="3" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="3" t="s">
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="B36" s="5"/>
       <c r="C36" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="D36" s="4" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
         <v>461</v>
       </c>
@@ -5254,34 +5272,35 @@
         <v>466</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
         <v>467</v>
       </c>
       <c r="B39" s="5"/>
-      <c r="C39" s="5" t="s">
+      <c r="C39" s="3" t="s">
         <v>468</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
         <v>470</v>
       </c>
       <c r="B40" s="5"/>
-      <c r="C40" s="3" t="s">
+      <c r="C40" s="5" t="s">
         <v>471</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="s">
+    <row r="41" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="3" t="s">
         <v>473</v>
       </c>
+      <c r="B41" s="5"/>
       <c r="C41" s="3" t="s">
         <v>474</v>
       </c>
@@ -5301,7 +5320,7 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="9" t="s">
+      <c r="A43" s="1" t="s">
         <v>479</v>
       </c>
       <c r="C43" s="3" t="s">
@@ -5322,7 +5341,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="9" t="s">
         <v>485</v>
       </c>
@@ -5333,7 +5352,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="9" t="s">
         <v>488</v>
       </c>
@@ -5344,7 +5363,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="9" t="s">
         <v>491</v>
       </c>
@@ -5366,8 +5385,8 @@
         <v>496</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1" t="s">
+    <row r="49" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="9" t="s">
         <v>497</v>
       </c>
       <c r="C49" s="3" t="s">
@@ -5375,6 +5394,17 @@
       </c>
       <c r="D49" s="3" t="s">
         <v>499</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>502</v>
       </c>
     </row>
   </sheetData>
@@ -5427,90 +5457,90 @@
     </row>
     <row r="5" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="168.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="220.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="231.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="210.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="314.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="112.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="199.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
     </row>
   </sheetData>

--- a/JP (Exclude Game)/Dialog/dialog.xlsx
+++ b/JP (Exclude Game)/Dialog/dialog.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" state="visible" r:id="rId3"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="528">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -1238,7 +1238,7 @@
 It is rumored that there's an ultimate artifact exclusive to your younger sisters.
 A ranch near Derphy can be highly profitable. 
 Tax will be lowered if your karma is high.
-Shopkeepers will pay more for monster's shit that weights more.
+Shopkeepers will pay more for monster shit that weighs more.
 Drinking cursed healing potions sometimes makes you sick.
 You *should* bless the hermes blood before drinking it!
 It would be really bad if something wrong happenes when you cast the return spell.</t>
@@ -1295,26 +1295,26 @@
 不明|もう…|もうだめぽ</t>
   </si>
   <si>
-    <t xml:space="preserve">Lucia|The Ship That Never Returned|If this bottle reaches someone,I will likely be beneath the sea by then.But the sky was very blue.
-An Unnamed Soldier|Final Letter|Fear weighed heavier than my sword.But I want someone to know I did not run.
-Ernes|Prayer of the Surf|God,if you cannot calm the waves,then at least grant me sleep.
-Mireille|The Promised Shore|If I arrive first,I will light a fire and wait.Come without losing your way.
-Navigator Daros|Record of the Stars|The stars were correct again today.The one who erred was me.
-Selena|A Small Confession|I could never speak your name aloud.That is my only regret.
-Old Man|To My Younger Days|The sea takes much,but nothing is entirely wasted.Survive.
-The Younger Twin|Half the World Left|Brother,half the world is still here.So please come back.
-Ship Doctor Renato|Medical Notes|I could not heal the wounds,but I eased the pain.That was enough.
-Isabelle|Finish the Song|Even if I am gone,please sing this song to the end.
-Smuggler Kyle|Where the Payment Lies|The gold is sunk in the northern cove.Dive if you want it.
-Acolyte Roa|Confession of Doubt|My prayers were unanswered.Still,I will not stop praying.
-Fisherman Hald|The Last Catch|There was no catch today.But I spoke with the sea.
-Traveler Cyan|A Passing Point|This is not the end.It is only a passing point.
-Royal Scribe|Excerpt from Official Records|The vessel was lost to the storm.End of report.
-Mother|To My Child|Put on your cloak when it gets cold.Promise me.
-Bard Fey|An Unfinished Poem|The rhyme is missing.To whoever finishes it.
-Mercenary Captain Volk|Order to Retreat|Come back alive.Honor can be picked up later.
-Little Girl|My First Journey|I'm a little scared.But it's fun.
-Someone|To Whoever Finds This|If you are reading this,the world is still going on.
+    <t xml:space="preserve">Lucia|The Ship That Never Returned|If this bottle reaches someone, I will likely be beneath the sea by then. But the sky was very blue.
+An Unnamed Soldier|Final Letter|Fear weighed heavier than my sword. But I want someone to know I did not run.
+Ernes|Prayer of the Surf|God, if you cannot calm the waves, then at least grant me sleep.
+Mireille|The Promised Shore|If I arrive first, I will light a fire and wait. Come without losing your way.
+Navigator Daros|Record of the Stars|The stars were correct again today. The one who erred was me.
+Selena|A Small Confession|I could never speak your name aloud. That is my only regret.
+Old Man|To My Younger Days|The sea takes much, but nothing is entirely wasted.Survive.
+The Younger Twin|Half the World Left|Brother, half the world is still here. So please come back.
+Ship Doctor Renato|Medical Notes|I could not heal the wounds, but I eased the pain. That was enough.
+Isabelle|Finish the Song|Even if I am gone, please sing this song to the end.
+Smuggler Kyle|Where the Payment Lies|The gold is sunk in the northern cove. Dive if you want it.
+Acolyte Roa|Confession of Doubt|My prayers were unanswered. Still, I will not stop praying.
+Fisherman Hald|The Last Catch|There was no catch today. But I spoke with the sea.
+Traveler Cyan|A Passing Point|This is not the end. It is only a passing point.
+Royal Scribe|Excerpt from Official Records|The vessel was lost to the storm. End of report.
+Mother|To My Child|Put on your cloak when it gets cold. Promise me.
+Bard Fey|An Unfinished Poem|The rhyme is missing. To whoever finishes it.
+Mercenary Captain Volk|Order to Retreat|Come back alive. Honor can be picked up later.
+Little Girl|My First Journey|I'm a little scared. But it's fun.
+Someone|To Whoever Finds This|If you are reading this, the world is still going on.
 Unknown|I...|I'm...going...home...!
 Unknown|I'm...|Moudamepo</t>
   </si>
@@ -1625,20 +1625,21 @@
     <t xml:space="preserve">mamani</t>
   </si>
   <si>
-    <t xml:space="preserve">人間の行動は、常に感情の誤作動に導かれる。
-機械はやがて人間の代わりに地上を支配するだろう。
+    <t xml:space="preserve">機械はやがて人間の代わりに地上を支配するだろう。
 あの戦狂いの祭壇は、いつからここにあるんだ？
 生身だった頃の私の体が、まだ地上に残っているようだ。
-くだらないな。人間界も、神界も。
-神という存在は非合理的だ。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Human behavior is always guided by the malfunction of emotion.
-One day, machines will rule the earth in place of humankind.
+神が全能など、戯言だと思わないか？
+世界に目的があると信じるのは自由だが、設計者の技量には期待しないことだ。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One day, machines will rule the earth in place of humankind.
 How long has that warmonger's altar been here?
 It seems my old body still remains on the surface.
-How absurd. The realm of humans, the realm of gods, all of it.
-The very existence of gods is irrational.</t>
+Surely you do not believe that gods are omnipotent?
+You are free to believe that the world has a purpose, but do not expect too much from its designer's competenc </t>
+  </si>
+  <si>
+    <t xml:space="preserve">mamani2</t>
   </si>
   <si>
     <t xml:space="preserve">namamani</t>
@@ -1901,7 +1902,7 @@
 いや…これはかぶりものではない。</t>
   </si>
   <si>
-    <t xml:space="preserve">The life of a merchant is nice and carefree, but it wouldn't be bad to settle down in a comfortable town somewhere. Yes, in Kapoor or thereabouts.
+    <t xml:space="preserve">The life of a merchant is nice and carefree, but it wouldn't be bad to settle down in a comfortable town somewhere. Yes, in Kapul or thereabouts.
 Is it rare to find a beastman merchant? Perhaps you don't see many of us in Tyris.
 We are proud of the many items we have gathered from Verizzia, the land of the oceans in the west, to Nieca, the golden land of the desert in the east. Take your time and look around.
 No...it's not a costume.</t>
@@ -3234,9 +3235,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>38</xdr:col>
-      <xdr:colOff>273960</xdr:colOff>
+      <xdr:colOff>272520</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>112680</xdr:rowOff>
+      <xdr:rowOff>111240</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3246,7 +3247,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="49653360" cy="112680"/>
+          <a:ext cx="49651920" cy="111240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4863,7 +4864,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.58"/>
@@ -4906,7 +4907,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>369</v>
       </c>
@@ -4917,494 +4918,505 @@
         <v>371</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>372</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>374</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
+      <c r="D8" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="C8" s="3" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9" t="s">
+      <c r="D9" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="C9" s="3" t="s">
+    </row>
+    <row r="10" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="9" t="s">
         <v>379</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+      <c r="D10" s="3" t="s">
         <v>381</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="C11" s="3" t="s">
+    </row>
+    <row r="12" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>386</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
+      <c r="D12" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="C12" s="3" t="s">
+    </row>
+    <row r="13" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="C13" s="3" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
+      <c r="D13" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="C13" s="3" t="s">
+    </row>
+    <row r="14" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>392</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
+      <c r="D14" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="C14" s="3" t="s">
+    </row>
+    <row r="15" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="C15" s="3" t="s">
         <v>395</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
+      <c r="D15" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="C15" s="3" t="s">
+    </row>
+    <row r="16" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="C16" s="3" t="s">
         <v>398</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
+      <c r="D16" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="C16" s="3" t="s">
+    </row>
+    <row r="17" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="C17" s="3" t="s">
         <v>401</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
+      <c r="D17" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="C17" s="3" t="s">
+    </row>
+    <row r="18" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="C18" s="3" t="s">
         <v>404</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
+      <c r="D18" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="C18" s="3" t="s">
+    </row>
+    <row r="19" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="C19" s="3" t="s">
         <v>407</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
+      <c r="D19" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="C19" s="3" t="s">
+    </row>
+    <row r="20" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="C20" s="3" t="s">
         <v>410</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
+      <c r="D20" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3" t="s">
+    </row>
+    <row r="21" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="B21" s="3"/>
+      <c r="C21" s="3" t="s">
         <v>413</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
+      <c r="D21" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="C21" s="3" t="s">
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="C22" s="3" t="s">
         <v>416</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="C22" s="3" t="s">
+    </row>
+    <row r="23" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="C23" s="3" t="s">
         <v>419</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
+      <c r="D23" s="3" t="s">
         <v>420</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>423</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="C25" s="3" t="s">
+    </row>
+    <row r="26" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="C26" s="3" t="s">
         <v>428</v>
       </c>
-    </row>
-    <row r="26" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
+      <c r="D26" s="3" t="s">
         <v>429</v>
       </c>
-      <c r="C26" s="3" t="s">
+    </row>
+    <row r="27" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="C27" s="3" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
+      <c r="D27" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="C27" s="3" t="s">
+    </row>
+    <row r="28" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="C28" s="3" t="s">
         <v>434</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
+      <c r="D28" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="C28" s="3" t="s">
+    </row>
+    <row r="29" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="C29" s="3" t="s">
         <v>437</v>
       </c>
-    </row>
-    <row r="29" customFormat="false" ht="79.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
+      <c r="D29" s="3" t="s">
         <v>438</v>
       </c>
-      <c r="C29" s="3" t="s">
+    </row>
+    <row r="30" customFormat="false" ht="79.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="D29" s="10" t="s">
+      <c r="C30" s="3" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="30" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
+      <c r="D30" s="10" t="s">
         <v>441</v>
       </c>
-      <c r="C30" s="3" t="s">
+    </row>
+    <row r="31" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="C31" s="3" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
+      <c r="D31" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="C31" s="10" t="s">
+    </row>
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="C32" s="10" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="32" customFormat="false" ht="179.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
+      <c r="D32" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="C32" s="3" t="s">
+    </row>
+    <row r="33" customFormat="false" ht="179.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="C33" s="3" t="s">
         <v>449</v>
       </c>
-    </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="9" t="s">
+      <c r="D33" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="C33" s="3" t="s">
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="9" t="s">
         <v>451</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="C34" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="9" t="s">
-        <v>452</v>
-      </c>
-      <c r="C34" s="11" t="s">
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="9" t="s">
         <v>453</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="C35" s="11" t="s">
         <v>454</v>
       </c>
-    </row>
-    <row r="35" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="9" t="s">
+      <c r="D35" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="C35" s="12" t="s">
+    </row>
+    <row r="36" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="9" t="s">
         <v>456</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="C36" s="12" t="s">
         <v>457</v>
       </c>
-    </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="s">
+      <c r="D36" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="C36" s="3" t="s">
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="C37" s="3" t="s">
         <v>460</v>
       </c>
-    </row>
-    <row r="37" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="3" t="s">
+      <c r="D37" s="4" t="s">
         <v>461</v>
       </c>
-      <c r="B37" s="5"/>
-      <c r="C37" s="3" t="s">
+    </row>
+    <row r="38" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="3" t="s">
         <v>462</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="3" t="s">
-        <v>464</v>
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="3" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="B40" s="5"/>
+      <c r="C40" s="3" t="s">
         <v>469</v>
       </c>
-    </row>
-    <row r="40" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="3" t="s">
+      <c r="D40" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5" t="s">
+    </row>
+    <row r="41" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="B41" s="5"/>
+      <c r="C41" s="5" t="s">
         <v>472</v>
       </c>
-    </row>
-    <row r="41" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="3" t="s">
+      <c r="D41" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="B41" s="5"/>
-      <c r="C41" s="3" t="s">
+    </row>
+    <row r="42" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="B42" s="5"/>
+      <c r="C42" s="3" t="s">
         <v>475</v>
       </c>
-    </row>
-    <row r="42" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="s">
+      <c r="D42" s="3" t="s">
         <v>476</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>477</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="D43" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="C43" s="3" t="s">
+    </row>
+    <row r="44" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="D43" s="3" t="s">
+      <c r="C44" s="3" t="s">
         <v>481</v>
       </c>
-    </row>
-    <row r="44" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="9" t="s">
+      <c r="D44" s="3" t="s">
         <v>482</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>483</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="9" t="s">
+        <v>483</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="D45" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="C45" s="3" t="s">
+    </row>
+    <row r="46" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="9" t="s">
         <v>486</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="C46" s="3" t="s">
         <v>487</v>
       </c>
-    </row>
-    <row r="46" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="9" t="s">
+      <c r="D46" s="3" t="s">
         <v>488</v>
       </c>
-      <c r="C46" s="3" t="s">
+    </row>
+    <row r="47" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="9" t="s">
         <v>489</v>
       </c>
-      <c r="D46" s="3" t="s">
+      <c r="C47" s="3" t="s">
         <v>490</v>
       </c>
-    </row>
-    <row r="47" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="9" t="s">
+      <c r="D47" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="C47" s="3" t="s">
+    </row>
+    <row r="48" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="9" t="s">
         <v>492</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="C48" s="3" t="s">
         <v>493</v>
       </c>
-    </row>
-    <row r="48" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="9" t="s">
+      <c r="D48" s="3" t="s">
         <v>494</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>495</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="D49" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="C49" s="3" t="s">
+    </row>
+    <row r="50" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="9" t="s">
         <v>498</v>
       </c>
-      <c r="D49" s="3" t="s">
+      <c r="C50" s="3" t="s">
         <v>499</v>
       </c>
-    </row>
-    <row r="50" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1" t="s">
+      <c r="D50" s="3" t="s">
         <v>500</v>
       </c>
-      <c r="C50" s="3" t="s">
+    </row>
+    <row r="51" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="D50" s="3" t="s">
+      <c r="C51" s="3" t="s">
         <v>502</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>503</v>
       </c>
     </row>
   </sheetData>
@@ -5457,90 +5469,90 @@
     </row>
     <row r="5" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="168.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="220.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="231.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="210.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="314.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="112.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="199.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
   </sheetData>
